--- a/server/api/offshore_forecast_api/models/substructure_feature_importance.xlsx
+++ b/server/api/offshore_forecast_api/models/substructure_feature_importance.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4537374377250671</v>
+        <v>0.3620563149452209</v>
       </c>
       <c r="C2" t="n">
-        <v>45.37374496459961</v>
+        <v>36.20563125610352</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1938129365444183</v>
+        <v>0.2624304890632629</v>
       </c>
       <c r="C3" t="n">
-        <v>19.38129425048828</v>
+        <v>26.24304962158203</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1809835284948349</v>
+        <v>0.211363360285759</v>
       </c>
       <c r="C4" t="n">
-        <v>18.09835243225098</v>
+        <v>21.1363353729248</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1714661121368408</v>
+        <v>0.1641498506069183</v>
       </c>
       <c r="C5" t="n">
-        <v>17.14661026000977</v>
+        <v>16.41498565673828</v>
       </c>
     </row>
   </sheetData>
